--- a/Xlsx/GlobalInt.xlsx
+++ b/Xlsx/GlobalInt.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21090" windowHeight="9165"/>
+    <workbookView windowWidth="21090" windowHeight="9720"/>
   </bookViews>
   <sheets>
     <sheet name="Property1" sheetId="1" r:id="rId1"/>
@@ -41,10 +41,10 @@
     <t>Type</t>
   </si>
   <si>
-    <t>int</t>
+    <t>Int</t>
   </si>
   <si>
-    <t>string</t>
+    <t>String</t>
   </si>
   <si>
     <t>Desc</t>

--- a/Xlsx/GlobalInt.xlsx
+++ b/Xlsx/GlobalInt.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21090" windowHeight="9720"/>
+    <workbookView windowWidth="21570" windowHeight="10890"/>
   </bookViews>
   <sheets>
     <sheet name="Property1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Id</t>
   </si>
@@ -35,16 +35,13 @@
     <t>Value</t>
   </si>
   <si>
-    <t>_Remark</t>
+    <t>#Remark</t>
   </si>
   <si>
     <t>Type</t>
   </si>
   <si>
     <t>Int</t>
-  </si>
-  <si>
-    <t>String</t>
   </si>
   <si>
     <t>Desc</t>
@@ -1229,24 +1226,21 @@
       <c r="B2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
+    </row>
+    <row r="3" s="3" customFormat="1" ht="14.25" spans="1:3">
+      <c r="A3" s="8" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" s="3" customFormat="1" ht="14.25" spans="1:3">
-      <c r="A3" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>8</v>
-      </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>99999</v>
@@ -1254,7 +1248,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>9999999</v>
@@ -1262,7 +1256,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6">
         <v>99999</v>
